--- a/data/trans_orig/P43D-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P43D-Edad-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>25259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>25259</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>35860</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56886</t>
+          <t>57260</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>35860</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56886</t>
+          <t>57260</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24713</t>
+          <t>25142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44406</t>
+          <t>43893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24713</t>
+          <t>25142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44406</t>
+          <t>43893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>31823</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56364</t>
+          <t>57286</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>31823</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56364</t>
+          <t>57286</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105439</t>
+          <t>107170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143146</t>
+          <t>144670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105439</t>
+          <t>107170</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143146</t>
+          <t>144670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90151</t>
+          <t>89337</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125122</t>
+          <t>124803</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90151</t>
+          <t>89337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125122</t>
+          <t>124803</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96834</t>
+          <t>95985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>133392</t>
+          <t>134332</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>96834</t>
+          <t>95985</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133392</t>
+          <t>134332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72247</t>
+          <t>72254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107482</t>
+          <t>108913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72247</t>
+          <t>72254</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107482</t>
+          <t>108913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>135836</t>
+          <t>133390</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>175116</t>
+          <t>173913</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>135836</t>
+          <t>133390</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>175116</t>
+          <t>173913</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>128538</t>
+          <t>127071</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171023</t>
+          <t>168053</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128538</t>
+          <t>127071</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>171023</t>
+          <t>168053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78061</t>
+          <t>79645</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112163</t>
+          <t>114510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78061</t>
+          <t>79645</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112163</t>
+          <t>114510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56340</t>
+          <t>57332</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87265</t>
+          <t>88416</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56340</t>
+          <t>57332</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87265</t>
+          <t>88416</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106260</t>
+          <t>106818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143672</t>
+          <t>143816</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106260</t>
+          <t>106818</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>143672</t>
+          <t>143816</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>120112</t>
+          <t>121167</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>120112</t>
+          <t>121167</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52512</t>
+          <t>52836</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80982</t>
+          <t>83448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52512</t>
+          <t>52836</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80982</t>
+          <t>83448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>73625</t>
+          <t>74856</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>103073</t>
+          <t>102190</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>73625</t>
+          <t>74856</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103073</t>
+          <t>102190</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59301</t>
+          <t>58650</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86912</t>
+          <t>86706</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59301</t>
+          <t>58650</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86912</t>
+          <t>86706</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32751</t>
+          <t>33709</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58010</t>
+          <t>58570</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32751</t>
+          <t>33709</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58010</t>
+          <t>58570</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25681</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25681</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>59745</t>
+          <t>60565</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>82091</t>
+          <t>82378</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>59745</t>
+          <t>60565</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82091</t>
+          <t>82378</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,59%</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26078</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>44218</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26078</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44218</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>28021</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>28021</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>45073</t>
+          <t>43918</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>57606</t>
+          <t>56744</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>45073</t>
+          <t>43918</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>57606</t>
+          <t>56744</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>89,36%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>388118</t>
+          <t>383297</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>459721</t>
+          <t>456740</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>388118</t>
+          <t>383297</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>459721</t>
+          <t>456740</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>515341</t>
+          <t>512955</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>596654</t>
+          <t>594393</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>515341</t>
+          <t>512955</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>596654</t>
+          <t>594393</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>430680</t>
+          <t>434950</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>505487</t>
+          <t>510469</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>430680</t>
+          <t>434950</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>505487</t>
+          <t>510469</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>298182</t>
+          <t>299895</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>364568</t>
+          <t>363947</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>298182</t>
+          <t>299895</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>364568</t>
+          <t>363947</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -3999,12 +3999,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -4077,12 +4077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64757</t>
+          <t>63993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64757</t>
+          <t>63993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42672</t>
+          <t>42556</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67678</t>
+          <t>67640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42672</t>
+          <t>42556</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67678</t>
+          <t>67640</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,41%</t>
         </is>
       </c>
     </row>
@@ -4233,12 +4233,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>44804</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69417</t>
+          <t>69261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>44804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69417</t>
+          <t>69261</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -4393,12 +4393,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31061</t>
+          <t>30673</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56330</t>
+          <t>55787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31061</t>
+          <t>30673</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56330</t>
+          <t>55787</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145678</t>
+          <t>147405</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187055</t>
+          <t>188360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>145678</t>
+          <t>147405</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>187055</t>
+          <t>188360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -4549,12 +4549,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119936</t>
+          <t>120617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160217</t>
+          <t>160374</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119936</t>
+          <t>120617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160217</t>
+          <t>160374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84169</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>119990</t>
+          <t>121335</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84169</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>119990</t>
+          <t>121335</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -4787,12 +4787,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65313</t>
+          <t>65253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99113</t>
+          <t>100800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65313</t>
+          <t>65253</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99113</t>
+          <t>100800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -4865,12 +4865,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>172017</t>
+          <t>171425</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>219942</t>
+          <t>216980</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>172017</t>
+          <t>171425</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>219942</t>
+          <t>216980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4915,12 +4915,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -4943,12 +4943,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151731</t>
+          <t>152885</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197284</t>
+          <t>194835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151731</t>
+          <t>152885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197284</t>
+          <t>194835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103113</t>
+          <t>107054</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145655</t>
+          <t>148484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103113</t>
+          <t>107054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145655</t>
+          <t>148484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64695</t>
+          <t>64292</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99699</t>
+          <t>101327</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64695</t>
+          <t>64292</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99699</t>
+          <t>101327</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -5259,12 +5259,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164079</t>
+          <t>163853</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211572</t>
+          <t>211928</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>164079</t>
+          <t>163853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>211572</t>
+          <t>211928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>130431</t>
+          <t>131670</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>174819</t>
+          <t>176728</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>130431</t>
+          <t>131670</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>174819</t>
+          <t>176728</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -5415,12 +5415,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54901</t>
+          <t>55617</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86867</t>
+          <t>89847</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54901</t>
+          <t>55617</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86867</t>
+          <t>89847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -5575,12 +5575,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>63875</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>96528</t>
+          <t>96030</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>63875</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>96528</t>
+          <t>96030</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>96697</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131745</t>
+          <t>133422</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>96697</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131745</t>
+          <t>133422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>42,2%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>66932</t>
+          <t>66389</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>99676</t>
+          <t>99901</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66932</t>
+          <t>66389</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>99676</t>
+          <t>99901</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>29069</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>53304</t>
+          <t>52266</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>29069</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>53304</t>
+          <t>52266</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>71578</t>
+          <t>70357</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>97464</t>
+          <t>97458</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6004,12 +6004,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>71578</t>
+          <t>70357</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>97464</t>
+          <t>97458</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37526</t>
+          <t>36877</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62814</t>
+          <t>61053</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37526</t>
+          <t>36877</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62814</t>
+          <t>61053</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6097,12 +6097,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -6125,12 +6125,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21171</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41996</t>
+          <t>40458</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21171</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>41996</t>
+          <t>40458</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -6203,12 +6203,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>24696</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>24696</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -6363,12 +6363,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>59599</t>
+          <t>61144</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>80910</t>
+          <t>81265</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>59599</t>
+          <t>61144</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>80910</t>
+          <t>81265</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>35853</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>35853</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -6597,12 +6597,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -6757,12 +6757,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>406009</t>
+          <t>409046</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>485969</t>
+          <t>488812</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>406009</t>
+          <t>409046</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>485969</t>
+          <t>488812</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>744514</t>
+          <t>740642</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>840524</t>
+          <t>837069</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>744514</t>
+          <t>740642</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>840524</t>
+          <t>837069</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>592669</t>
+          <t>597123</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>681823</t>
+          <t>681811</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>592669</t>
+          <t>597123</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>681823</t>
+          <t>681811</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -6991,12 +6991,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>380150</t>
+          <t>378136</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>456811</t>
+          <t>454248</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>380150</t>
+          <t>378136</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>456811</t>
+          <t>454248</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16860</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7340,12 +7340,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16860</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -7403,12 +7403,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47131</t>
+          <t>47713</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70717</t>
+          <t>70954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47131</t>
+          <t>47713</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70717</t>
+          <t>70954</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7453,12 +7453,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -7481,12 +7481,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51279</t>
+          <t>49833</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74583</t>
+          <t>74617</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51279</t>
+          <t>49833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74583</t>
+          <t>74617</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24152</t>
+          <t>24227</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>44100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24152</t>
+          <t>24227</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>44100</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33216</t>
+          <t>33747</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58161</t>
+          <t>57480</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33216</t>
+          <t>33747</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58161</t>
+          <t>57480</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -7797,12 +7797,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151528</t>
+          <t>151129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188964</t>
+          <t>188340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7832,12 +7832,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151528</t>
+          <t>151129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>188964</t>
+          <t>188340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,82%</t>
         </is>
       </c>
     </row>
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93328</t>
+          <t>93154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127770</t>
+          <t>127344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7890,12 +7890,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7910,12 +7910,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93328</t>
+          <t>93154</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127770</t>
+          <t>127344</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -7953,12 +7953,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42141</t>
+          <t>42486</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67904</t>
+          <t>68847</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7988,12 +7988,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42141</t>
+          <t>42486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67904</t>
+          <t>68847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46909</t>
+          <t>47338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74997</t>
+          <t>74294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8128,12 +8128,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46909</t>
+          <t>47338</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74997</t>
+          <t>74294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -8191,12 +8191,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>226940</t>
+          <t>227203</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>272179</t>
+          <t>272051</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>226940</t>
+          <t>227203</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>272179</t>
+          <t>272051</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8241,12 +8241,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101670</t>
+          <t>102315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142543</t>
+          <t>138823</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101670</t>
+          <t>102315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142543</t>
+          <t>138823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -8347,12 +8347,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72196</t>
+          <t>73063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105850</t>
+          <t>106561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72196</t>
+          <t>73063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105850</t>
+          <t>106561</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -8507,12 +8507,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77406</t>
+          <t>76514</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113265</t>
+          <t>112283</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8522,12 +8522,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77406</t>
+          <t>76514</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113265</t>
+          <t>112283</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -8585,12 +8585,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202346</t>
+          <t>204748</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245940</t>
+          <t>246871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8600,12 +8600,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8620,12 +8620,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>202346</t>
+          <t>204748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245940</t>
+          <t>246871</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8635,12 +8635,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -8663,12 +8663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>93944</t>
+          <t>96923</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>130674</t>
+          <t>132653</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8698,12 +8698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93944</t>
+          <t>96923</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130674</t>
+          <t>132653</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -8741,12 +8741,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46890</t>
+          <t>46788</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77878</t>
+          <t>75131</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46890</t>
+          <t>46788</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77878</t>
+          <t>75131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75876</t>
+          <t>76780</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>110974</t>
+          <t>110639</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>75876</t>
+          <t>76780</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>110974</t>
+          <t>110639</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -8979,12 +8979,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>129132</t>
+          <t>128651</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>167979</t>
+          <t>166544</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9014,12 +9014,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129132</t>
+          <t>128651</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>167979</t>
+          <t>166544</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9029,12 +9029,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -9057,12 +9057,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41215</t>
+          <t>40548</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>69749</t>
+          <t>68367</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41215</t>
+          <t>40548</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69749</t>
+          <t>68367</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -9135,12 +9135,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>25038</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>50529</t>
+          <t>48215</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9170,12 +9170,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>25038</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>50529</t>
+          <t>48215</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -9295,12 +9295,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>108246</t>
+          <t>109155</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138114</t>
+          <t>137452</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>108246</t>
+          <t>109155</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>138114</t>
+          <t>137452</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,6%</t>
         </is>
       </c>
     </row>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47214</t>
+          <t>45589</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74304</t>
+          <t>72282</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>47214</t>
+          <t>45589</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>74304</t>
+          <t>72282</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -9451,12 +9451,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32901</t>
+          <t>32758</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>32901</t>
+          <t>32758</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -9529,12 +9529,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20192</t>
+          <t>20695</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20192</t>
+          <t>20695</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -9689,12 +9689,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>91845</t>
+          <t>92034</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>115905</t>
+          <t>115940</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>91845</t>
+          <t>92034</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>115905</t>
+          <t>115940</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -9767,12 +9767,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>31786</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>31786</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -9845,12 +9845,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>24068</t>
+          <t>23897</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9860,12 +9860,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>24068</t>
+          <t>23897</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9895,12 +9895,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -10083,12 +10083,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>491110</t>
+          <t>491489</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>573159</t>
+          <t>571532</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10118,12 +10118,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>491110</t>
+          <t>491489</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>573159</t>
+          <t>571532</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>885927</t>
+          <t>885668</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>978449</t>
+          <t>977905</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>885927</t>
+          <t>885668</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>978449</t>
+          <t>977905</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -10239,12 +10239,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>454403</t>
+          <t>458077</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>534084</t>
+          <t>537375</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>454403</t>
+          <t>458077</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>534084</t>
+          <t>537375</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -10317,12 +10317,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>250943</t>
+          <t>251512</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>315189</t>
+          <t>311983</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10332,12 +10332,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>250943</t>
+          <t>251512</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>315189</t>
+          <t>311983</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10367,12 +10367,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -10646,32 +10646,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10681,32 +10681,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -10724,12 +10724,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10739,17 +10739,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10774,17 +10774,17 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -10802,32 +10802,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10837,32 +10837,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>58,59%</t>
         </is>
       </c>
     </row>
@@ -10880,32 +10880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21480</t>
+          <t>22795</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10915,32 +10915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21480</t>
+          <t>22795</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -10958,17 +10958,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89078</t>
+          <t>24342</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22475</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>177158</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89078</t>
+          <t>24342</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22475</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>177158</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -11118,32 +11118,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>75055</t>
+          <t>83207</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33293</t>
+          <t>69878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113050</t>
+          <t>96670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11153,32 +11153,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75055</t>
+          <t>83207</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33293</t>
+          <t>69878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113050</t>
+          <t>96670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -11196,32 +11196,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41291</t>
+          <t>43848</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>31438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63895</t>
+          <t>56845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11231,32 +11231,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41291</t>
+          <t>43848</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>31438</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63895</t>
+          <t>56845</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -11274,32 +11274,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39499</t>
+          <t>40147</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60750</t>
+          <t>53878</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11309,32 +11309,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39499</t>
+          <t>40147</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60750</t>
+          <t>53878</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -11352,17 +11352,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11387,17 +11387,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11434,32 +11434,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>49636</t>
+          <t>55219</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40055</t>
+          <t>44967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61183</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11469,32 +11469,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49636</t>
+          <t>55219</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40055</t>
+          <t>44967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61183</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -11512,32 +11512,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>96415</t>
+          <t>108374</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85657</t>
+          <t>94314</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111160</t>
+          <t>122978</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11547,32 +11547,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96415</t>
+          <t>108374</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85657</t>
+          <t>94314</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111160</t>
+          <t>122978</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -11590,32 +11590,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>59438</t>
+          <t>69816</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47360</t>
+          <t>57190</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69884</t>
+          <t>83449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11625,32 +11625,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59438</t>
+          <t>69816</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47360</t>
+          <t>57190</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69884</t>
+          <t>83449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -11668,32 +11668,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>48239</t>
+          <t>54136</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>43644</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59327</t>
+          <t>67074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11703,32 +11703,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48239</t>
+          <t>54136</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>43644</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59327</t>
+          <t>67074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -11746,17 +11746,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>253728</t>
+          <t>287544</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>253728</t>
+          <t>287544</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>253728</t>
+          <t>287544</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>253728</t>
+          <t>287544</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>253728</t>
+          <t>287544</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>253728</t>
+          <t>287544</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11828,32 +11828,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94503</t>
+          <t>65957</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63080</t>
+          <t>54685</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>179441</t>
+          <t>77177</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11863,32 +11863,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>94503</t>
+          <t>65957</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63080</t>
+          <t>54685</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179441</t>
+          <t>77177</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -11906,32 +11906,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>134202</t>
+          <t>141736</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101825</t>
+          <t>126372</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155471</t>
+          <t>156772</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11941,32 +11941,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>134202</t>
+          <t>141736</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101825</t>
+          <t>126372</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>155471</t>
+          <t>156772</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -11984,32 +11984,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>98211</t>
+          <t>103979</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72211</t>
+          <t>90343</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>115653</t>
+          <t>118011</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12019,32 +12019,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>98211</t>
+          <t>103979</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72211</t>
+          <t>90343</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>115653</t>
+          <t>118011</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -12062,32 +12062,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>60004</t>
+          <t>67742</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43353</t>
+          <t>57169</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72921</t>
+          <t>80620</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12097,32 +12097,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>60004</t>
+          <t>67742</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43353</t>
+          <t>57169</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72921</t>
+          <t>80620</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -12140,17 +12140,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>386920</t>
+          <t>379414</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>386920</t>
+          <t>379414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>386920</t>
+          <t>379414</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12175,17 +12175,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>386920</t>
+          <t>379414</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>386920</t>
+          <t>379414</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386920</t>
+          <t>379414</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12222,32 +12222,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>75433</t>
+          <t>80836</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>68507</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87274</t>
+          <t>95282</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12257,32 +12257,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>75433</t>
+          <t>80836</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>68507</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87274</t>
+          <t>95282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -12300,27 +12300,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>110996</t>
+          <t>123689</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99356</t>
+          <t>110242</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124085</t>
+          <t>137072</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12335,27 +12335,27 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>110996</t>
+          <t>123689</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99356</t>
+          <t>110242</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>124085</t>
+          <t>137072</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -12378,32 +12378,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>64934</t>
+          <t>73202</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53925</t>
+          <t>62049</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75007</t>
+          <t>85364</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12413,32 +12413,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>64934</t>
+          <t>73202</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53925</t>
+          <t>62049</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75007</t>
+          <t>85364</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -12456,32 +12456,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>36373</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25926</t>
+          <t>27515</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>45913</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12491,32 +12491,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>36373</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25926</t>
+          <t>27515</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>45913</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -12534,17 +12534,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12569,17 +12569,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12616,32 +12616,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>93643</t>
+          <t>100569</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>84574</t>
+          <t>90692</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>103873</t>
+          <t>110703</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12651,32 +12651,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>93643</t>
+          <t>100569</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84574</t>
+          <t>90692</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>103873</t>
+          <t>110703</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>51,8%</t>
         </is>
       </c>
     </row>
@@ -12694,32 +12694,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>59783</t>
+          <t>65631</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50516</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>69117</t>
+          <t>76269</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12729,32 +12729,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>59783</t>
+          <t>65631</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>50516</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>69117</t>
+          <t>76269</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -12772,32 +12772,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>27264</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34828</t>
+          <t>38739</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12807,32 +12807,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>27264</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>34828</t>
+          <t>38739</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -12850,32 +12850,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>12380</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12885,32 +12885,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>12380</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -12928,17 +12928,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>195763</t>
+          <t>213717</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>195763</t>
+          <t>213717</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>195763</t>
+          <t>213717</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12963,17 +12963,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>195763</t>
+          <t>213717</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>195763</t>
+          <t>213717</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>195763</t>
+          <t>213717</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13010,32 +13010,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>135382</t>
+          <t>146116</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>128662</t>
+          <t>138548</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>141441</t>
+          <t>152805</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13045,32 +13045,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>135382</t>
+          <t>146116</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>128662</t>
+          <t>138548</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>141441</t>
+          <t>152805</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -13088,32 +13088,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>18436</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13123,32 +13123,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>18436</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -13166,32 +13166,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -13244,17 +13244,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>420</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13279,17 +13279,17 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>420</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -13322,17 +13322,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>156614</t>
+          <t>170094</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>156614</t>
+          <t>170094</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>156614</t>
+          <t>170094</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13357,17 +13357,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>156614</t>
+          <t>170094</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>156614</t>
+          <t>170094</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>156614</t>
+          <t>170094</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13404,32 +13404,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>539022</t>
+          <t>478520</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>466406</t>
+          <t>449858</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>677370</t>
+          <t>513326</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -13439,32 +13439,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>539022</t>
+          <t>478520</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>466406</t>
+          <t>449858</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>677370</t>
+          <t>513326</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -13482,32 +13482,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>498418</t>
+          <t>545931</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>433308</t>
+          <t>515344</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>541739</t>
+          <t>578355</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -13517,32 +13517,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>498418</t>
+          <t>545931</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>433308</t>
+          <t>515344</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>541739</t>
+          <t>578355</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -13560,32 +13560,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>318388</t>
+          <t>350108</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>271802</t>
+          <t>324297</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>351039</t>
+          <t>379849</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -13595,32 +13595,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>318388</t>
+          <t>350108</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>271802</t>
+          <t>324297</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>351039</t>
+          <t>379849</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -13638,32 +13638,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>209630</t>
+          <t>229778</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>176144</t>
+          <t>204682</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>237727</t>
+          <t>255878</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -13673,32 +13673,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>209630</t>
+          <t>229778</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>176144</t>
+          <t>204682</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>237727</t>
+          <t>255878</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -13716,17 +13716,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -13751,17 +13751,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
